--- a/AAII_Financials/Quarterly/MDIBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MDIBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="92">
   <si>
     <t>MDIBY</t>
   </si>
@@ -656,70 +656,73 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
-        <v>45291</v>
-      </c>
-      <c r="L7" s="2">
-        <v>45199</v>
-      </c>
-      <c r="M7" s="2">
-        <v>45107</v>
-      </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -759,8 +762,11 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -800,8 +806,11 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -841,8 +850,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -858,8 +870,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -899,8 +912,11 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -940,8 +956,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -981,8 +1000,11 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1022,8 +1044,11 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1036,8 +1061,9 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1077,8 +1103,11 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1118,8 +1147,11 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1135,8 +1167,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1176,8 +1209,11 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1217,8 +1253,11 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1258,8 +1297,11 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1299,8 +1341,11 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1340,8 +1385,11 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1381,8 +1429,11 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1422,8 +1473,11 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1463,8 +1517,11 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1504,8 +1561,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1545,8 +1605,11 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1586,8 +1649,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1627,8 +1693,11 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1668,8 +1737,11 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1709,8 +1781,11 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1750,8 +1825,11 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1791,54 +1869,60 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
-        <v>45291</v>
-      </c>
-      <c r="L38" s="2">
-        <v>45199</v>
-      </c>
-      <c r="M38" s="2">
-        <v>45107</v>
-      </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1854,8 +1938,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1871,377 +1956,405 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E41" s="3">
+      <c r="D41" s="3">
+        <v>1693600</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F41" s="3">
         <v>1214000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
+        <v>1214000</v>
+      </c>
+      <c r="H41" s="3">
         <v>2159700</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J41" s="3">
         <v>3601400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
+        <v>4625500</v>
+      </c>
+      <c r="L41" s="3">
         <v>5243000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N41" s="3">
         <v>4625500</v>
       </c>
-      <c r="K41" s="3">
-        <v>5243000</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M41" s="3">
-        <v>4625500</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P41" s="3">
         <v>11124200</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>28012200</v>
+      </c>
+      <c r="E42" s="3">
         <v>19838800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>31438800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
+        <v>31438800</v>
+      </c>
+      <c r="H42" s="3">
         <v>20651800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>17134300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>24133500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
+        <v>16483900</v>
+      </c>
+      <c r="L42" s="3">
         <v>19360900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="M42" s="3">
+        <v>10995100</v>
+      </c>
+      <c r="N42" s="3">
         <v>16483900</v>
       </c>
-      <c r="K42" s="3">
-        <v>19360900</v>
-      </c>
-      <c r="L42" s="3">
-        <v>10995100</v>
-      </c>
-      <c r="M42" s="3">
-        <v>16483900</v>
-      </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>14814600</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E43" s="3">
+      <c r="D43" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3">
         <v>1564700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
+        <v>1564700</v>
+      </c>
+      <c r="H43" s="3">
         <v>148500</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3">
         <v>1199700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
+        <v>1013300</v>
+      </c>
+      <c r="L43" s="3">
         <v>163400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N43" s="3">
         <v>1013300</v>
       </c>
-      <c r="K43" s="3">
-        <v>163400</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M43" s="3">
-        <v>1013300</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3">
         <v>123900</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E44" s="3">
+      <c r="D44" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>11200</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="G44" s="3">
+        <v>11200</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
         <v>9500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
+        <v>5900</v>
+      </c>
+      <c r="L44" s="3">
         <v>8400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3">
         <v>5900</v>
       </c>
-      <c r="K44" s="3">
-        <v>8400</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M44" s="3">
-        <v>5900</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3">
         <v>1285500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
+        <v>1285500</v>
+      </c>
+      <c r="H45" s="3">
         <v>1612200</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3">
         <v>79900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
+        <v>356200</v>
+      </c>
+      <c r="L45" s="3">
         <v>445800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>356200</v>
       </c>
-      <c r="K45" s="3">
-        <v>445800</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M45" s="3">
-        <v>356200</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3">
         <v>365100</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>30163800</v>
+      </c>
+      <c r="E46" s="3">
         <v>19838800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>36262700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
+        <v>36262700</v>
+      </c>
+      <c r="H46" s="3">
         <v>24902600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>17134300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>29797500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
+        <v>23407600</v>
+      </c>
+      <c r="L46" s="3">
         <v>26026400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="M46" s="3">
+        <v>10995100</v>
+      </c>
+      <c r="N46" s="3">
         <v>23407600</v>
       </c>
-      <c r="K46" s="3">
-        <v>26026400</v>
-      </c>
-      <c r="L46" s="3">
-        <v>10995100</v>
-      </c>
-      <c r="M46" s="3">
-        <v>23407600</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P46" s="3">
         <v>26789500</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>12051700</v>
+      </c>
+      <c r="E47" s="3">
         <v>34321600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>11911900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
+        <v>11911900</v>
+      </c>
+      <c r="H47" s="3">
         <v>12339000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>30277000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>12299200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
+        <v>11319100</v>
+      </c>
+      <c r="L47" s="3">
         <v>11937300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="M47" s="3">
+        <v>30231700</v>
+      </c>
+      <c r="N47" s="3">
         <v>11319100</v>
       </c>
-      <c r="K47" s="3">
-        <v>11937300</v>
-      </c>
-      <c r="L47" s="3">
-        <v>30231700</v>
-      </c>
-      <c r="M47" s="3">
-        <v>11319100</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P47" s="3">
         <v>7874800</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>932100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1985800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>591600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
+        <v>591600</v>
+      </c>
+      <c r="H48" s="3">
         <v>547200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1778400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>528000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
+        <v>518400</v>
+      </c>
+      <c r="L48" s="3">
         <v>536300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3">
+        <v>1410900</v>
+      </c>
+      <c r="N48" s="3">
         <v>518400</v>
       </c>
-      <c r="K48" s="3">
-        <v>536300</v>
-      </c>
-      <c r="L48" s="3">
-        <v>1410900</v>
-      </c>
-      <c r="M48" s="3">
-        <v>518400</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P48" s="3">
         <v>488400</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>1174400</v>
       </c>
       <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>1277300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
+        <v>1277300</v>
+      </c>
+      <c r="H49" s="3">
         <v>1098600</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>1120100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
+        <v>869800</v>
+      </c>
+      <c r="L49" s="3">
         <v>1221100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>869800</v>
       </c>
-      <c r="K49" s="3">
-        <v>1221100</v>
-      </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
-      <c r="M49" s="3">
-        <v>869800</v>
-      </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>898700</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2281,8 +2394,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2322,49 +2438,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4274400</v>
+      </c>
+      <c r="E52" s="3">
         <v>2701500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>584700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
+        <v>584700</v>
+      </c>
+      <c r="H52" s="3">
         <v>1758200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>2257000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>141200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
+        <v>134400</v>
+      </c>
+      <c r="L52" s="3">
         <v>1402400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="M52" s="3">
+        <v>3325700</v>
+      </c>
+      <c r="N52" s="3">
         <v>134400</v>
       </c>
-      <c r="K52" s="3">
-        <v>1402400</v>
-      </c>
-      <c r="L52" s="3">
-        <v>3325700</v>
-      </c>
-      <c r="M52" s="3">
-        <v>134400</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P52" s="3">
         <v>1101300</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2404,49 +2526,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>125329300</v>
+      </c>
+      <c r="E54" s="3">
         <v>122707400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>122369100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
+        <v>122369100</v>
+      </c>
+      <c r="H54" s="3">
         <v>103438900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>109486500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>106317700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
+        <v>100026000</v>
+      </c>
+      <c r="L54" s="3">
         <v>104908100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
+        <v>100043000</v>
+      </c>
+      <c r="N54" s="3">
         <v>100026000</v>
       </c>
-      <c r="K54" s="3">
-        <v>104908100</v>
-      </c>
-      <c r="L54" s="3">
-        <v>100043000</v>
-      </c>
-      <c r="M54" s="3">
-        <v>100026000</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P54" s="3">
         <v>100179300</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2462,8 +2590,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2479,254 +2608,273 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>36609100</v>
+      </c>
+      <c r="E57" s="3">
         <v>36479900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>37585200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
+        <v>37585200</v>
+      </c>
+      <c r="H57" s="3">
         <v>32219300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>31402200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>31495800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
+        <v>32994000</v>
+      </c>
+      <c r="L57" s="3">
         <v>33073000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="M57" s="3">
+        <v>29184700</v>
+      </c>
+      <c r="N57" s="3">
         <v>32994000</v>
       </c>
-      <c r="K57" s="3">
-        <v>33073000</v>
-      </c>
-      <c r="L57" s="3">
-        <v>29184700</v>
-      </c>
-      <c r="M57" s="3">
-        <v>32994000</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P57" s="3">
         <v>33722100</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>20444600</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>17714200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
+        <v>17714200</v>
+      </c>
+      <c r="H58" s="3">
         <v>16402400</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>17231900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
+        <v>12508500</v>
+      </c>
+      <c r="L58" s="3">
         <v>16478000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>12508500</v>
       </c>
-      <c r="K58" s="3">
-        <v>16478000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
-        <v>12508500</v>
-      </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>15214100</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6536800</v>
+      </c>
+      <c r="E59" s="3">
         <v>21348800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7012300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
+        <v>7012300</v>
+      </c>
+      <c r="H59" s="3">
         <v>5223300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>23132700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>6174700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
+        <v>5373800</v>
+      </c>
+      <c r="L59" s="3">
         <v>5342400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="M59" s="3">
+        <v>18998400</v>
+      </c>
+      <c r="N59" s="3">
         <v>5373800</v>
       </c>
-      <c r="K59" s="3">
-        <v>5342400</v>
-      </c>
-      <c r="L59" s="3">
-        <v>18998400</v>
-      </c>
-      <c r="M59" s="3">
-        <v>5373800</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3">
         <v>4946400</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>63603700</v>
+      </c>
+      <c r="E60" s="3">
         <v>57828700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>62957500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
+        <v>62957500</v>
+      </c>
+      <c r="H60" s="3">
         <v>53853700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>54534900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>55427200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
+        <v>51320300</v>
+      </c>
+      <c r="L60" s="3">
         <v>54893300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="M60" s="3">
+        <v>48183100</v>
+      </c>
+      <c r="N60" s="3">
         <v>51320300</v>
       </c>
-      <c r="K60" s="3">
-        <v>54893300</v>
-      </c>
-      <c r="L60" s="3">
-        <v>48183100</v>
-      </c>
-      <c r="M60" s="3">
-        <v>51320300</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P60" s="3">
         <v>54236000</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>45940500</v>
+      </c>
+      <c r="E61" s="3">
         <v>47189500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>44603400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
+        <v>44603400</v>
+      </c>
+      <c r="H61" s="3">
         <v>35899000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>37838100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>36322800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
+        <v>35130900</v>
+      </c>
+      <c r="L61" s="3">
         <v>35575600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="M61" s="3">
+        <v>34560300</v>
+      </c>
+      <c r="N61" s="3">
         <v>35130900</v>
       </c>
-      <c r="K61" s="3">
-        <v>35575600</v>
-      </c>
-      <c r="L61" s="3">
-        <v>34560300</v>
-      </c>
-      <c r="M61" s="3">
-        <v>35130900</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>34584900</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1990000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4409100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>919400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
+        <v>919400</v>
+      </c>
+      <c r="H62" s="3">
         <v>1547600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>4706400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>2081400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
+        <v>582900</v>
+      </c>
+      <c r="L62" s="3">
         <v>1767500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="M62" s="3">
+        <v>5713600</v>
+      </c>
+      <c r="N62" s="3">
         <v>582900</v>
       </c>
-      <c r="K62" s="3">
-        <v>1767500</v>
-      </c>
-      <c r="L62" s="3">
-        <v>5713600</v>
-      </c>
-      <c r="M62" s="3">
-        <v>582900</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3">
         <v>375400</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2766,8 +2914,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2807,8 +2958,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2848,49 +3002,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>112084100</v>
+      </c>
+      <c r="E66" s="3">
         <v>109427300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>109007500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
+        <v>109007500</v>
+      </c>
+      <c r="H66" s="3">
         <v>91718000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>97079400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>94271000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
+        <v>87548300</v>
+      </c>
+      <c r="L66" s="3">
         <v>92689500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3">
+        <v>88457000</v>
+      </c>
+      <c r="N66" s="3">
         <v>87548300</v>
       </c>
-      <c r="K66" s="3">
-        <v>92689500</v>
-      </c>
-      <c r="L66" s="3">
-        <v>88457000</v>
-      </c>
-      <c r="M66" s="3">
-        <v>87548300</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P66" s="3">
         <v>89806800</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2906,8 +3066,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2947,8 +3108,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2988,8 +3152,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3029,8 +3196,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3070,49 +3240,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10641300</v>
+      </c>
+      <c r="E72" s="3">
         <v>341700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1563700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
+        <v>1563700</v>
+      </c>
+      <c r="H72" s="3">
         <v>683000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>368100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1364400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
+        <v>1120100</v>
+      </c>
+      <c r="L72" s="3">
         <v>9650600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
+        <v>371800</v>
+      </c>
+      <c r="N72" s="3">
         <v>1120100</v>
       </c>
-      <c r="K72" s="3">
-        <v>9650600</v>
-      </c>
-      <c r="L72" s="3">
-        <v>371800</v>
-      </c>
-      <c r="M72" s="3">
-        <v>1120100</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3">
         <v>8154500</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3152,8 +3328,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3193,8 +3372,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3234,49 +3416,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13227900</v>
+      </c>
+      <c r="E76" s="3">
         <v>13263600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13345100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
+        <v>13345100</v>
+      </c>
+      <c r="H76" s="3">
         <v>11631700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>12312200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>11954400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
+        <v>12364000</v>
+      </c>
+      <c r="L76" s="3">
         <v>12112100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3">
+        <v>11485100</v>
+      </c>
+      <c r="N76" s="3">
         <v>12364000</v>
       </c>
-      <c r="K76" s="3">
-        <v>12112100</v>
-      </c>
-      <c r="L76" s="3">
-        <v>11485100</v>
-      </c>
-      <c r="M76" s="3">
-        <v>12364000</v>
-      </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10433400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10262800</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3316,54 +3504,60 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
-        <v>45291</v>
-      </c>
-      <c r="L80" s="2">
-        <v>45199</v>
-      </c>
-      <c r="M80" s="2">
-        <v>45107</v>
-      </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3403,8 +3597,11 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3420,8 +3617,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3461,8 +3659,11 @@
       <c r="O83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3502,8 +3703,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3543,8 +3747,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3584,8 +3791,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3625,8 +3835,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3666,8 +3879,11 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3707,8 +3923,11 @@
       <c r="O89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3724,8 +3943,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3765,8 +3985,11 @@
       <c r="O91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3806,8 +4029,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3847,8 +4073,11 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3888,8 +4117,11 @@
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3905,8 +4137,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3946,8 +4179,11 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3987,8 +4223,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4028,8 +4267,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4069,8 +4311,11 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4110,8 +4355,11 @@
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4151,8 +4399,11 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4190,6 +4441,9 @@
         <v>4</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
